--- a/client/dist/student-template.xlsx
+++ b/client/dist/student-template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Students" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -32,13 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="6">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="58" formatCode="m/d/yy"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -69,8 +64,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,7 +398,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:K4"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" customWidth="1"/>
+    <col min="11" max="11" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,50 +424,138 @@
         <v>Date of Birth</v>
       </c>
       <c r="D1" t="str">
+        <v>Roll No</v>
+      </c>
+      <c r="E1" t="str">
         <v>Grade Level</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>Section</v>
+      </c>
+      <c r="G1" t="str">
         <v>Parent Name</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>Parent Phone</v>
       </c>
-      <c r="G1" t="str">
-        <v>Section</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Roll No</v>
+      <c r="I1" t="str">
+        <v>Mother's Name</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Address</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Aadhaar Card Number</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ABC</v>
+        <v>Aarav Sharma</v>
       </c>
       <c r="B2" t="str">
         <v>Male</v>
       </c>
-      <c r="C2" t="str">
-        <v>15/01/2001</v>
-      </c>
-      <c r="D2" t="str">
-        <v>1st Venus</v>
+      <c r="C2" s="1" t="str">
+        <v>15-05-2010</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>ABCD</v>
+        <v>6</v>
       </c>
       <c r="F2" t="str">
-        <v>00000000000</v>
+        <v>A</v>
       </c>
       <c r="G2" t="str">
-        <v>Venus</v>
+        <v>Rajesh Sharma</v>
       </c>
       <c r="H2" t="str">
-        <v>01</v>
+        <v>9876543210</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Sunita Sharma</v>
+      </c>
+      <c r="J2" t="str">
+        <v>123, Model Town, Delhi</v>
+      </c>
+      <c r="K2" t="str">
+        <v>123456789012</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Priya Singh</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Female</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <v>22-08-2011</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>6</v>
+      </c>
+      <c r="F3" t="str">
+        <v>A</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Mohan Singh</v>
+      </c>
+      <c r="H3" t="str">
+        <v>9876500011</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Rekha Singh</v>
+      </c>
+      <c r="J3" t="str">
+        <v>45, Civil Lines, Delhi</v>
+      </c>
+      <c r="K3" t="str">
+        <v>234567890123</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Rohan Verma</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Male</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <v>03-01-2012</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="str">
+        <v>6</v>
+      </c>
+      <c r="F4" t="str">
+        <v>B</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Anil Verma</v>
+      </c>
+      <c r="H4" t="str">
+        <v>9812345678</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Kavita Verma</v>
+      </c>
+      <c r="J4" t="str">
+        <v>78, Rohini, Delhi</v>
+      </c>
+      <c r="K4" t="str">
+        <v>345678901234</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
   </ignoredErrors>
 </worksheet>
 </file>